--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8F0786-767E-41FB-BBBE-D74BBF5A54F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4444E0-7430-488A-9749-D115B3908A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel2/Terminefussball_2026_Herbst.xlsx
+++ b/Excel2/Terminefussball_2026_Herbst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4444E0-7430-488A-9749-D115B3908A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E25862-C9C5-47ED-BE7C-5B7F224CCD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nach Mannschaften sortiert" sheetId="1" r:id="rId1"/>
@@ -3603,9 +3603,9 @@
       <c r="I66" s="16"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="e">
-        <f>#REF!+1</f>
-        <v>#REF!</v>
+      <c r="A67" s="6">
+        <f t="shared" si="1"/>
+        <v>66</v>
       </c>
       <c r="B67" s="6">
         <v>1</v>
@@ -3622,9 +3622,9 @@
       <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="e">
+      <c r="A68" s="6">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>67</v>
       </c>
       <c r="B68" s="6">
         <v>2</v>
@@ -3641,9 +3641,9 @@
       <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="e">
+      <c r="A69" s="6">
         <f t="shared" si="1"/>
-        <v>#REF!</v>
+        <v>68</v>
       </c>
       <c r="B69" s="6">
         <v>3</v>
@@ -3660,9 +3660,9 @@
       <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="e">
+      <c r="A70" s="6">
         <f t="shared" ref="A70:A101" si="2">A69+1</f>
-        <v>#REF!</v>
+        <v>69</v>
       </c>
       <c r="B70" s="6">
         <v>4</v>
@@ -3679,9 +3679,9 @@
       <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="e">
+      <c r="A71" s="6">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>70</v>
       </c>
       <c r="B71" s="6">
         <v>5</v>
@@ -3698,9 +3698,9 @@
       <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="e">
+      <c r="A72" s="6">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>71</v>
       </c>
       <c r="B72" s="6">
         <v>6</v>
@@ -3717,9 +3717,9 @@
       <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="e">
+      <c r="A73" s="6">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>72</v>
       </c>
       <c r="B73" s="6">
         <v>7</v>
@@ -3736,9 +3736,9 @@
       <c r="H73" s="6"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="e">
+      <c r="A74" s="6">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>73</v>
       </c>
       <c r="B74" s="6">
         <v>8</v>
@@ -3755,9 +3755,9 @@
       <c r="H74" s="6"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="e">
+      <c r="A75" s="6">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>74</v>
       </c>
       <c r="B75" s="6">
         <v>9</v>
@@ -3774,9 +3774,9 @@
       <c r="H75" s="6"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="e">
+      <c r="A76" s="6">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>75</v>
       </c>
       <c r="B76" s="6">
         <v>10</v>
@@ -3793,9 +3793,9 @@
       <c r="H76" s="6"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="88" t="e">
+      <c r="A77" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>76</v>
       </c>
       <c r="B77" s="88">
         <v>1</v>
@@ -3812,9 +3812,9 @@
       <c r="H77" s="88"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="88" t="e">
+      <c r="A78" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>77</v>
       </c>
       <c r="B78" s="88">
         <v>2</v>
@@ -3831,9 +3831,9 @@
       <c r="H78" s="88"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="88" t="e">
+      <c r="A79" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>78</v>
       </c>
       <c r="B79" s="88">
         <v>3</v>
@@ -3850,9 +3850,9 @@
       <c r="H79" s="88"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="88" t="e">
+      <c r="A80" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>79</v>
       </c>
       <c r="B80" s="88">
         <v>4</v>
@@ -3869,9 +3869,9 @@
       <c r="H80" s="88"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="88" t="e">
+      <c r="A81" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>80</v>
       </c>
       <c r="B81" s="88">
         <v>5</v>
@@ -3888,9 +3888,9 @@
       <c r="H81" s="88"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="88" t="e">
+      <c r="A82" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>81</v>
       </c>
       <c r="B82" s="88">
         <v>6</v>
@@ -3907,9 +3907,9 @@
       <c r="H82" s="88"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="88" t="e">
+      <c r="A83" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>82</v>
       </c>
       <c r="B83" s="88">
         <v>7</v>
@@ -3926,9 +3926,9 @@
       <c r="H83" s="88"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="88" t="e">
+      <c r="A84" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>83</v>
       </c>
       <c r="B84" s="88">
         <v>8</v>
@@ -3945,9 +3945,9 @@
       <c r="H84" s="88"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="88" t="e">
+      <c r="A85" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>84</v>
       </c>
       <c r="B85" s="88">
         <v>9</v>
@@ -3964,9 +3964,9 @@
       <c r="H85" s="88"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="88" t="e">
+      <c r="A86" s="88">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>85</v>
       </c>
       <c r="B86" s="88">
         <v>10</v>
@@ -3983,9 +3983,9 @@
       <c r="H86" s="88"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="19" t="e">
+      <c r="A87" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>86</v>
       </c>
       <c r="B87" s="19">
         <v>1</v>
@@ -4002,9 +4002,9 @@
       <c r="H87" s="19"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="19" t="e">
+      <c r="A88" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>87</v>
       </c>
       <c r="B88" s="19">
         <v>2</v>
@@ -4021,9 +4021,9 @@
       <c r="H88" s="19"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="19" t="e">
+      <c r="A89" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>88</v>
       </c>
       <c r="B89" s="19">
         <v>3</v>
@@ -4040,9 +4040,9 @@
       <c r="H89" s="19"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="19" t="e">
+      <c r="A90" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>89</v>
       </c>
       <c r="B90" s="19">
         <v>4</v>
@@ -4059,9 +4059,9 @@
       <c r="H90" s="19"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="19" t="e">
+      <c r="A91" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>90</v>
       </c>
       <c r="B91" s="19">
         <v>5</v>
@@ -4078,9 +4078,9 @@
       <c r="H91" s="19"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="19" t="e">
+      <c r="A92" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>91</v>
       </c>
       <c r="B92" s="19">
         <v>6</v>
@@ -4097,9 +4097,9 @@
       <c r="H92" s="19"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="19" t="e">
+      <c r="A93" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="B93" s="19">
         <v>7</v>
@@ -4116,9 +4116,9 @@
       <c r="H93" s="19"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="19" t="e">
+      <c r="A94" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>93</v>
       </c>
       <c r="B94" s="19">
         <v>8</v>
@@ -4135,9 +4135,9 @@
       <c r="H94" s="19"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="19" t="e">
+      <c r="A95" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>94</v>
       </c>
       <c r="B95" s="19">
         <v>9</v>
@@ -4154,9 +4154,9 @@
       <c r="H95" s="19"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="19" t="e">
+      <c r="A96" s="19">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>95</v>
       </c>
       <c r="B96" s="19">
         <v>10</v>
@@ -4173,9 +4173,9 @@
       <c r="H96" s="19"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="85" t="e">
+      <c r="A97" s="85">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>96</v>
       </c>
       <c r="B97" s="85">
         <v>1</v>
@@ -4200,9 +4200,9 @@
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="85" t="e">
+      <c r="A98" s="85">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>97</v>
       </c>
       <c r="B98" s="85">
         <v>2</v>
@@ -4219,9 +4219,9 @@
       <c r="H98" s="85"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="85" t="e">
+      <c r="A99" s="85">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>98</v>
       </c>
       <c r="B99" s="85">
         <v>3</v>
@@ -4238,9 +4238,9 @@
       <c r="H99" s="85"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="85" t="e">
+      <c r="A100" s="85">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>99</v>
       </c>
       <c r="B100" s="85">
         <v>4</v>
@@ -4257,9 +4257,9 @@
       <c r="H100" s="85"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="85" t="e">
+      <c r="A101" s="85">
         <f t="shared" si="2"/>
-        <v>#REF!</v>
+        <v>100</v>
       </c>
       <c r="B101" s="85">
         <v>5</v>
@@ -4276,9 +4276,9 @@
       <c r="H101" s="85"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="8" t="e">
+      <c r="A102" s="8">
         <f t="shared" ref="A102:A133" si="3">A101+1</f>
-        <v>#REF!</v>
+        <v>101</v>
       </c>
       <c r="B102" s="8">
         <v>1</v>
@@ -4295,9 +4295,9 @@
       <c r="H102" s="8"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="8" t="e">
+      <c r="A103" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>102</v>
       </c>
       <c r="B103" s="8">
         <v>2</v>
@@ -4314,9 +4314,9 @@
       <c r="H103" s="8"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="e">
+      <c r="A104" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>103</v>
       </c>
       <c r="B104" s="8">
         <v>3</v>
@@ -4333,9 +4333,9 @@
       <c r="H104" s="8"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="8" t="e">
+      <c r="A105" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>104</v>
       </c>
       <c r="B105" s="8">
         <v>4</v>
@@ -4352,9 +4352,9 @@
       <c r="H105" s="8"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="8" t="e">
+      <c r="A106" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>105</v>
       </c>
       <c r="B106" s="8">
         <v>5</v>
@@ -4371,9 +4371,9 @@
       <c r="H106" s="8"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="8" t="e">
+      <c r="A107" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>106</v>
       </c>
       <c r="B107" s="8">
         <v>6</v>
@@ -4390,9 +4390,9 @@
       <c r="H107" s="8"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="8" t="e">
+      <c r="A108" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>107</v>
       </c>
       <c r="B108" s="8">
         <v>7</v>
@@ -4409,9 +4409,9 @@
       <c r="H108" s="8"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="8" t="e">
+      <c r="A109" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>108</v>
       </c>
       <c r="B109" s="8">
         <v>8</v>
@@ -4428,9 +4428,9 @@
       <c r="H109" s="8"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="8" t="e">
+      <c r="A110" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>109</v>
       </c>
       <c r="B110" s="8">
         <v>9</v>
@@ -4447,9 +4447,9 @@
       <c r="H110" s="8"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="8" t="e">
+      <c r="A111" s="8">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>110</v>
       </c>
       <c r="B111" s="8">
         <v>10</v>
@@ -4466,9 +4466,9 @@
       <c r="H111" s="8"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="25" t="e">
+      <c r="A112" s="25">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>111</v>
       </c>
       <c r="B112" s="25">
         <v>1</v>
@@ -4493,9 +4493,9 @@
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="25" t="e">
+      <c r="A113" s="25">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>112</v>
       </c>
       <c r="B113" s="25">
         <v>2</v>
@@ -4512,9 +4512,9 @@
       <c r="H113" s="25"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="25" t="e">
+      <c r="A114" s="25">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>113</v>
       </c>
       <c r="B114" s="25">
         <v>3</v>
@@ -4531,9 +4531,9 @@
       <c r="H114" s="25"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="25" t="e">
+      <c r="A115" s="25">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>114</v>
       </c>
       <c r="B115" s="25">
         <v>4</v>
@@ -4550,9 +4550,9 @@
       <c r="H115" s="25"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="25" t="e">
+      <c r="A116" s="25">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>115</v>
       </c>
       <c r="B116" s="25">
         <v>5</v>
@@ -4569,9 +4569,9 @@
       <c r="H116" s="25"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="42" t="e">
+      <c r="A117" s="42">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>116</v>
       </c>
       <c r="B117" s="42">
         <v>1</v>
@@ -4588,9 +4588,9 @@
       <c r="H117" s="42"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="42" t="e">
+      <c r="A118" s="42">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>117</v>
       </c>
       <c r="B118" s="42">
         <v>2</v>
@@ -4607,9 +4607,9 @@
       <c r="H118" s="42"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="42" t="e">
+      <c r="A119" s="42">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>118</v>
       </c>
       <c r="B119" s="42">
         <v>3</v>
@@ -4626,9 +4626,9 @@
       <c r="H119" s="42"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="42" t="e">
+      <c r="A120" s="42">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>119</v>
       </c>
       <c r="B120" s="42">
         <v>4</v>
@@ -4645,9 +4645,9 @@
       <c r="H120" s="42"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="42" t="e">
+      <c r="A121" s="42">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>120</v>
       </c>
       <c r="B121" s="42">
         <v>5</v>
@@ -4664,9 +4664,9 @@
       <c r="H121" s="42"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="30" t="e">
+      <c r="A122" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>121</v>
       </c>
       <c r="B122" s="30">
         <v>1</v>
@@ -4691,9 +4691,9 @@
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="30" t="e">
+      <c r="A123" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>122</v>
       </c>
       <c r="B123" s="30">
         <v>2</v>
@@ -4718,9 +4718,9 @@
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="30" t="e">
+      <c r="A124" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>123</v>
       </c>
       <c r="B124" s="30">
         <v>3</v>
@@ -4745,9 +4745,9 @@
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="30" t="e">
+      <c r="A125" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>124</v>
       </c>
       <c r="B125" s="30">
         <v>4</v>
@@ -4772,9 +4772,9 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="30" t="e">
+      <c r="A126" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>125</v>
       </c>
       <c r="B126" s="30">
         <v>5</v>
@@ -4799,9 +4799,9 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="30" t="e">
+      <c r="A127" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>126</v>
       </c>
       <c r="B127" s="30">
         <v>6</v>
@@ -4826,9 +4826,9 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="30" t="e">
+      <c r="A128" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>127</v>
       </c>
       <c r="B128" s="30">
         <v>7</v>
@@ -4853,9 +4853,9 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="30" t="e">
+      <c r="A129" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>128</v>
       </c>
       <c r="B129" s="30">
         <v>8</v>
@@ -4880,9 +4880,9 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="30" t="e">
+      <c r="A130" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>129</v>
       </c>
       <c r="B130" s="30">
         <v>9</v>
@@ -4907,9 +4907,9 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="30" t="e">
+      <c r="A131" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>130</v>
       </c>
       <c r="B131" s="30">
         <v>10</v>
@@ -4934,9 +4934,9 @@
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="30" t="e">
+      <c r="A132" s="30">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>131</v>
       </c>
       <c r="B132" s="30">
         <v>11</v>
@@ -4961,9 +4961,9 @@
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="40" t="e">
+      <c r="A133" s="40">
         <f t="shared" si="3"/>
-        <v>#REF!</v>
+        <v>132</v>
       </c>
       <c r="B133" s="40">
         <v>2</v>
@@ -4988,9 +4988,9 @@
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="54" t="e">
+      <c r="A134" s="54">
         <f t="shared" ref="A134:A141" si="4">A133+1</f>
-        <v>#REF!</v>
+        <v>133</v>
       </c>
       <c r="B134" s="54">
         <v>1</v>
@@ -5015,9 +5015,9 @@
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="54" t="e">
+      <c r="A135" s="54">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
+        <v>134</v>
       </c>
       <c r="B135" s="54">
         <v>2</v>
@@ -5042,9 +5042,9 @@
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" s="54" t="e">
+      <c r="A136" s="54">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
+        <v>135</v>
       </c>
       <c r="B136" s="54">
         <v>3</v>
@@ -5069,9 +5069,9 @@
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" s="54" t="e">
+      <c r="A137" s="54">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
+        <v>136</v>
       </c>
       <c r="B137" s="54">
         <v>0</v>
@@ -5096,9 +5096,9 @@
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" s="54" t="e">
+      <c r="A138" s="54">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
+        <v>137</v>
       </c>
       <c r="B138" s="54">
         <v>4</v>
@@ -5123,9 +5123,9 @@
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="54" t="e">
+      <c r="A139" s="54">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
+        <v>138</v>
       </c>
       <c r="B139" s="54">
         <v>5</v>
@@ -5150,9 +5150,9 @@
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="54" t="e">
+      <c r="A140" s="54">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
+        <v>139</v>
       </c>
       <c r="B140" s="54">
         <v>6</v>
@@ -5177,9 +5177,9 @@
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" s="54" t="e">
+      <c r="A141" s="54">
         <f t="shared" si="4"/>
-        <v>#REF!</v>
+        <v>140</v>
       </c>
       <c r="B141" s="54">
         <v>0</v>
@@ -18795,9 +18795,9 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="54" t="e">
+      <c r="A7" s="54">
         <f>'Nach Mannschaften sortiert'!A67</f>
-        <v>#REF!</v>
+        <v>66</v>
       </c>
       <c r="B7" s="54">
         <f>'Nach Mannschaften sortiert'!B67</f>
@@ -18863,9 +18863,9 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="52" t="e">
+      <c r="A9" s="52">
         <f>'Nach Mannschaften sortiert'!A122</f>
-        <v>#REF!</v>
+        <v>121</v>
       </c>
       <c r="B9" s="52">
         <f>'Nach Mannschaften sortiert'!B122</f>
@@ -18931,9 +18931,9 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="52" t="e">
+      <c r="A11" s="52">
         <f>'Nach Mannschaften sortiert'!A123</f>
-        <v>#REF!</v>
+        <v>122</v>
       </c>
       <c r="B11" s="52">
         <f>'Nach Mannschaften sortiert'!B123</f>
@@ -19033,9 +19033,9 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="52" t="e">
+      <c r="A14" s="52">
         <f>'Nach Mannschaften sortiert'!A124</f>
-        <v>#REF!</v>
+        <v>123</v>
       </c>
       <c r="B14" s="52">
         <f>'Nach Mannschaften sortiert'!B124</f>
@@ -19373,9 +19373,9 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="50" t="e">
+      <c r="A24" s="50">
         <f>'Nach Mannschaften sortiert'!A102</f>
-        <v>#REF!</v>
+        <v>101</v>
       </c>
       <c r="B24" s="50">
         <f>'Nach Mannschaften sortiert'!B102</f>
@@ -19441,9 +19441,9 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="50" t="e">
+      <c r="A26" s="50">
         <f>'Nach Mannschaften sortiert'!A112</f>
-        <v>#REF!</v>
+        <v>111</v>
       </c>
       <c r="B26" s="50">
         <f>'Nach Mannschaften sortiert'!B112</f>
@@ -19543,9 +19543,9 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="50" t="e">
+      <c r="A29" s="50">
         <f>'Nach Mannschaften sortiert'!A117</f>
-        <v>#REF!</v>
+        <v>116</v>
       </c>
       <c r="B29" s="50">
         <f>'Nach Mannschaften sortiert'!B117</f>
@@ -19747,9 +19747,9 @@
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="50" t="e">
+      <c r="A35" s="50">
         <f>'Nach Mannschaften sortiert'!A88</f>
-        <v>#REF!</v>
+        <v>87</v>
       </c>
       <c r="B35" s="50">
         <f>'Nach Mannschaften sortiert'!B88</f>
@@ -19985,9 +19985,9 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="54" t="e">
+      <c r="A42" s="54">
         <f>'Nach Mannschaften sortiert'!A92</f>
-        <v>#REF!</v>
+        <v>91</v>
       </c>
       <c r="B42" s="54">
         <f>'Nach Mannschaften sortiert'!B92</f>
@@ -20053,9 +20053,9 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="50" t="e">
+      <c r="A44" s="50">
         <f>'Nach Mannschaften sortiert'!A69</f>
-        <v>#REF!</v>
+        <v>68</v>
       </c>
       <c r="B44" s="50">
         <f>'Nach Mannschaften sortiert'!B69</f>
@@ -20155,9 +20155,9 @@
       </c>
     </row>
     <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="54" t="e">
+      <c r="A47" s="54">
         <f>'Nach Mannschaften sortiert'!A68</f>
-        <v>#REF!</v>
+        <v>67</v>
       </c>
       <c r="B47" s="54">
         <f>'Nach Mannschaften sortiert'!B68</f>
@@ -20223,9 +20223,9 @@
       </c>
     </row>
     <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="54" t="e">
+      <c r="A49" s="54">
         <f>'Nach Mannschaften sortiert'!A70</f>
-        <v>#REF!</v>
+        <v>69</v>
       </c>
       <c r="B49" s="54">
         <f>'Nach Mannschaften sortiert'!B70</f>
@@ -20257,9 +20257,9 @@
       </c>
     </row>
     <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="54" t="e">
+      <c r="A50" s="54">
         <f>'Nach Mannschaften sortiert'!A71</f>
-        <v>#REF!</v>
+        <v>70</v>
       </c>
       <c r="B50" s="54">
         <f>'Nach Mannschaften sortiert'!B71</f>
@@ -20359,9 +20359,9 @@
       </c>
     </row>
     <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="54" t="e">
+      <c r="A53" s="54">
         <f>'Nach Mannschaften sortiert'!A73</f>
-        <v>#REF!</v>
+        <v>72</v>
       </c>
       <c r="B53" s="54">
         <f>'Nach Mannschaften sortiert'!B73</f>
@@ -20427,9 +20427,9 @@
       </c>
     </row>
     <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="54" t="e">
+      <c r="A55" s="54">
         <f>'Nach Mannschaften sortiert'!A87</f>
-        <v>#REF!</v>
+        <v>86</v>
       </c>
       <c r="B55" s="54">
         <f>'Nach Mannschaften sortiert'!B87</f>
@@ -20461,9 +20461,9 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="48" t="e">
+      <c r="A56" s="48">
         <f>'Nach Mannschaften sortiert'!A93</f>
-        <v>#REF!</v>
+        <v>92</v>
       </c>
       <c r="B56" s="48">
         <f>'Nach Mannschaften sortiert'!B93</f>
@@ -20495,9 +20495,9 @@
       </c>
     </row>
     <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="54" t="e">
+      <c r="A57" s="54">
         <f>'Nach Mannschaften sortiert'!A90</f>
-        <v>#REF!</v>
+        <v>89</v>
       </c>
       <c r="B57" s="54">
         <f>'Nach Mannschaften sortiert'!B90</f>
@@ -20631,9 +20631,9 @@
       </c>
     </row>
     <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="54" t="e">
+      <c r="A61" s="54">
         <f>'Nach Mannschaften sortiert'!A94</f>
-        <v>#REF!</v>
+        <v>93</v>
       </c>
       <c r="B61" s="54">
         <f>'Nach Mannschaften sortiert'!B94</f>
@@ -20699,9 +20699,9 @@
       </c>
     </row>
     <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="54" t="e">
+      <c r="A63" s="54">
         <f>'Nach Mannschaften sortiert'!A96</f>
-        <v>#REF!</v>
+        <v>95</v>
       </c>
       <c r="B63" s="54">
         <f>'Nach Mannschaften sortiert'!B96</f>
@@ -20767,9 +20767,9 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="48" t="e">
+      <c r="A65" s="48">
         <f>'Nach Mannschaften sortiert'!A95</f>
-        <v>#REF!</v>
+        <v>94</v>
       </c>
       <c r="B65" s="48">
         <f>'Nach Mannschaften sortiert'!B95</f>
@@ -20799,9 +20799,9 @@
       </c>
     </row>
     <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="54" t="e">
+      <c r="A66" s="54">
         <f>'Nach Mannschaften sortiert'!A103</f>
-        <v>#REF!</v>
+        <v>102</v>
       </c>
       <c r="B66" s="54">
         <f>'Nach Mannschaften sortiert'!B103</f>
@@ -20833,9 +20833,9 @@
       </c>
     </row>
     <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="54" t="e">
+      <c r="A67" s="54">
         <f>'Nach Mannschaften sortiert'!A104</f>
-        <v>#REF!</v>
+        <v>103</v>
       </c>
       <c r="B67" s="54">
         <f>'Nach Mannschaften sortiert'!B104</f>
@@ -20867,9 +20867,9 @@
       </c>
     </row>
     <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="54" t="e">
+      <c r="A68" s="54">
         <f>'Nach Mannschaften sortiert'!A105</f>
-        <v>#REF!</v>
+        <v>104</v>
       </c>
       <c r="B68" s="54">
         <f>'Nach Mannschaften sortiert'!B105</f>
@@ -20901,9 +20901,9 @@
       </c>
     </row>
     <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="54" t="e">
+      <c r="A69" s="54">
         <f>'Nach Mannschaften sortiert'!A111</f>
-        <v>#REF!</v>
+        <v>110</v>
       </c>
       <c r="B69" s="54">
         <f>'Nach Mannschaften sortiert'!B111</f>
@@ -20935,9 +20935,9 @@
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="48" t="e">
+      <c r="A70" s="48">
         <f>'Nach Mannschaften sortiert'!A72</f>
-        <v>#REF!</v>
+        <v>71</v>
       </c>
       <c r="B70" s="48">
         <f>'Nach Mannschaften sortiert'!B72</f>
@@ -20969,9 +20969,9 @@
       </c>
     </row>
     <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="54" t="e">
+      <c r="A71" s="54">
         <f>'Nach Mannschaften sortiert'!A113</f>
-        <v>#REF!</v>
+        <v>112</v>
       </c>
       <c r="B71" s="54">
         <f>'Nach Mannschaften sortiert'!B113</f>
@@ -21003,9 +21003,9 @@
       </c>
     </row>
     <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="54" t="e">
+      <c r="A72" s="54">
         <f>'Nach Mannschaften sortiert'!A114</f>
-        <v>#REF!</v>
+        <v>113</v>
       </c>
       <c r="B72" s="54">
         <f>'Nach Mannschaften sortiert'!B114</f>
@@ -21037,9 +21037,9 @@
       </c>
     </row>
     <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="54" t="e">
+      <c r="A73" s="54">
         <f>'Nach Mannschaften sortiert'!A115</f>
-        <v>#REF!</v>
+        <v>114</v>
       </c>
       <c r="B73" s="54">
         <f>'Nach Mannschaften sortiert'!B115</f>
@@ -21071,9 +21071,9 @@
       </c>
     </row>
     <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="54" t="e">
+      <c r="A74" s="54">
         <f>'Nach Mannschaften sortiert'!A116</f>
-        <v>#REF!</v>
+        <v>115</v>
       </c>
       <c r="B74" s="54">
         <f>'Nach Mannschaften sortiert'!B116</f>
@@ -21139,9 +21139,9 @@
       </c>
     </row>
     <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="54" t="e">
+      <c r="A76" s="54">
         <f>'Nach Mannschaften sortiert'!A118</f>
-        <v>#REF!</v>
+        <v>117</v>
       </c>
       <c r="B76" s="54">
         <f>'Nach Mannschaften sortiert'!B118</f>
@@ -21173,9 +21173,9 @@
       </c>
     </row>
     <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="54" t="e">
+      <c r="A77" s="54">
         <f>'Nach Mannschaften sortiert'!A119</f>
-        <v>#REF!</v>
+        <v>118</v>
       </c>
       <c r="B77" s="54">
         <f>'Nach Mannschaften sortiert'!B119</f>
@@ -21207,9 +21207,9 @@
       </c>
     </row>
     <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="54" t="e">
+      <c r="A78" s="54">
         <f>'Nach Mannschaften sortiert'!A120</f>
-        <v>#REF!</v>
+        <v>119</v>
       </c>
       <c r="B78" s="54">
         <f>'Nach Mannschaften sortiert'!B120</f>
@@ -21241,9 +21241,9 @@
       </c>
     </row>
     <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="54" t="e">
+      <c r="A79" s="54">
         <f>'Nach Mannschaften sortiert'!A121</f>
-        <v>#REF!</v>
+        <v>120</v>
       </c>
       <c r="B79" s="54">
         <f>'Nach Mannschaften sortiert'!B121</f>
@@ -21275,9 +21275,9 @@
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="48" t="e">
+      <c r="A80" s="48">
         <f>'Nach Mannschaften sortiert'!A74</f>
-        <v>#REF!</v>
+        <v>73</v>
       </c>
       <c r="B80" s="48">
         <f>'Nach Mannschaften sortiert'!B74</f>
@@ -21411,9 +21411,9 @@
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="54" t="e">
+      <c r="A84" s="54">
         <f>'Nach Mannschaften sortiert'!A133</f>
-        <v>#REF!</v>
+        <v>132</v>
       </c>
       <c r="B84" s="54">
         <f>'Nach Mannschaften sortiert'!B133</f>
